--- a/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 0,0</t>
+          <t>-12,41; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 0,0</t>
+          <t>-10,09; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 12,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 15,54</t>
+          <t>2,75; 15,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,14</t>
+          <t>-3,92; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 25,32</t>
+          <t>-0,11; 24,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,54</t>
+          <t>-7,08; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 1,57</t>
+          <t>-15,23; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,47; —</t>
+          <t>-55,89; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 0,0</t>
+          <t>-8,2; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,17</t>
+          <t>0,42; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,0</t>
+          <t>-2,66; 2,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,44</t>
+          <t>-2,55; 1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 1034,65</t>
+          <t>-15,6; 1149,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 267,22</t>
+          <t>-80,37; 296,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,0</t>
+          <t>-11,94; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 0,0</t>
+          <t>-11,31; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,18</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,65</t>
+          <t>2,62; 14,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 7,67</t>
+          <t>-4,03; 7,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 24,85</t>
+          <t>1,29; 26,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 4,03</t>
+          <t>-6,03; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 1,61</t>
+          <t>-15,0; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,89; —</t>
+          <t>-19,71; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 0,0</t>
+          <t>-8,19; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,81</t>
+          <t>0,1; 7,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,2</t>
+          <t>-2,81; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,45</t>
+          <t>-2,34; 1,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 1149,58</t>
+          <t>-26,19; 921,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 296,93</t>
+          <t>-81,02; 224,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 0,0</t>
+          <t>-9,53; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 0,0</t>
+          <t>-11,8; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,62</t>
+          <t>2,69; 15,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 7,33</t>
+          <t>-3,81; 7,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 26,13</t>
+          <t>1,8; 25,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 4,4</t>
+          <t>-6,53; 4,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 1,38</t>
+          <t>-14,78; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,71; —</t>
+          <t>-26,47; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 0,0</t>
+          <t>-8,71; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,33</t>
+          <t>0,23; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,84</t>
+          <t>-2,73; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,56</t>
+          <t>-2,4; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 921,61</t>
+          <t>-18,0; 1034,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 224,58</t>
+          <t>-80,03; 267,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.4355268422598204</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.8389919819738656</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8590775278923718</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,53; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,8; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,85</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.195054976067055</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.937142487140774</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.004427835861277</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,69; 15,54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 7,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.486125412048914</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.471411015029316</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.8085866519972789</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>11,59</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>297,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-71,64%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5616561253791514</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.8413034592369787</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 25,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,53; 4,54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,78; 1,57</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-26,47; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.309614234082817</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.179552704160774</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +741,205 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.913379263079376</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1793473167499346</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.844199203899312</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>2.094134426031786</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1984395595739476</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.6822994522861076</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,71; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.2783958402716838</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.18219680849681</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.136186535514429</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.5026506641662104</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.719475326828061</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.218457939158216</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3625808652970456</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3298006319358533</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.657623221382603</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-22,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 7,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 2,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 1,44</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,0; 1034,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-80,03; 267,22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.6216972025075763</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.08204580963323541</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.02673525807112931</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1.652150151299655</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1503399011240426</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.09656382904025769</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.05467612923172458</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.666113260052693</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4986557574116259</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.2285161137855906</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7963926186874642</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.325547767870172</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.524977063116544</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3360738048872841</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>10.98124204969509</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.530104026763215</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +948,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
